--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.5462,0.3444,0.0144,0.0629</t>
-  </si>
-  <si>
-    <t>0.0177,0.0053,0.0032,0.9887</t>
-  </si>
-  <si>
-    <t>0.8292,0.0498,0.0320,0.0625</t>
-  </si>
-  <si>
-    <t>0.0518,0.0037,0.0014,0.9797</t>
-  </si>
-  <si>
-    <t>0.9883,0.0009,0.0001,0.0072</t>
-  </si>
-  <si>
-    <t>0.9873,0.0011,0.0002,0.0070</t>
-  </si>
-  <si>
-    <t>0.9832,0.0046,0.0011,0.0044</t>
-  </si>
-  <si>
-    <t>0.9745,0.0038,0.0029,0.0101</t>
-  </si>
-  <si>
-    <t>0.9820,0.0032,0.0005,0.0070</t>
-  </si>
-  <si>
-    <t>0.9840,0.0028,0.0002,0.0073</t>
-  </si>
-  <si>
-    <t>0.9864,0.0023,0.0004,0.0056</t>
-  </si>
-  <si>
-    <t>0.9802,0.0009,0.0001,0.0162</t>
-  </si>
-  <si>
-    <t>0.2580,0.1156,0.6816,0.0161</t>
-  </si>
-  <si>
-    <t>0.1404,0.0238,0.8731,0.0021</t>
-  </si>
-  <si>
-    <t>0.2257,0.0773,0.6469,0.0021</t>
-  </si>
-  <si>
-    <t>0.0414,0.0129,0.9593,0.0024</t>
-  </si>
-  <si>
-    <t>0.3301,0.1002,0.6641,0.0547</t>
-  </si>
-  <si>
-    <t>0.2190,0.8715,0.0060,0.0014</t>
-  </si>
-  <si>
-    <t>0.2455,0.8569,0.0063,0.0024</t>
-  </si>
-  <si>
-    <t>0.7696,0.3413,0.0045,0.0058</t>
-  </si>
-  <si>
-    <t>0.6268,0.5853,0.0078,0.0033</t>
-  </si>
-  <si>
-    <t>0.0807,0.9552,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.1518,0.0187,0.8277,0.0285</t>
-  </si>
-  <si>
-    <t>0.0822,0.0166,0.8945,0.0170</t>
-  </si>
-  <si>
-    <t>0.0083,0.0049,0.9773,0.0081</t>
-  </si>
-  <si>
-    <t>0.2300,0.0841,0.6737,0.0466</t>
-  </si>
-  <si>
-    <t>0.0527,0.0033,0.9375,0.0150</t>
-  </si>
-  <si>
-    <t>0.1639,0.0167,0.8574,0.0070</t>
-  </si>
-  <si>
-    <t>0.0175,0.0058,0.9755,0.0061</t>
-  </si>
-  <si>
-    <t>0.4420,0.6166,0.0323,0.0059</t>
-  </si>
-  <si>
-    <t>0.1355,0.0096,0.9084,0.0074</t>
-  </si>
-  <si>
-    <t>0.0006,0.0019,0.9880,0.0312</t>
-  </si>
-  <si>
-    <t>0.0202,0.7614,0.4751,0.0016</t>
-  </si>
-  <si>
-    <t>0.7356,0.1149,0.1310,0.0643</t>
-  </si>
-  <si>
-    <t>0.3148,0.1211,0.6193,0.0793</t>
-  </si>
-  <si>
-    <t>0.7886,0.3084,0.0098,0.0060</t>
-  </si>
-  <si>
-    <t>0.1398,0.8221,0.1014,0.0418</t>
-  </si>
-  <si>
-    <t>0.0592,0.3808,0.6373,0.0546</t>
-  </si>
-  <si>
-    <t>0.0387,0.2601,0.8788,0.0078</t>
-  </si>
-  <si>
-    <t>0.0217,0.0204,0.8830,0.1197</t>
-  </si>
-  <si>
-    <t>0.0833,0.0081,0.5525,0.3992</t>
-  </si>
-  <si>
-    <t>0.0217,0.0176,0.9722,0.0020</t>
-  </si>
-  <si>
-    <t>0.0119,0.8945,0.3343,0.0058</t>
-  </si>
-  <si>
-    <t>0.0372,0.1802,0.8882,0.0079</t>
-  </si>
-  <si>
-    <t>0.1830,0.1142,0.1417,0.7603</t>
-  </si>
-  <si>
-    <t>0.0123,0.9709,0.0154,0.0042</t>
-  </si>
-  <si>
-    <t>0.0074,0.9654,0.0572,0.0014</t>
-  </si>
-  <si>
-    <t>0.0077,0.9746,0.0369,0.0036</t>
-  </si>
-  <si>
-    <t>0.0028,0.7057,0.9003,0.0024</t>
-  </si>
-  <si>
-    <t>0.0009,0.0716,0.9922,0.0010</t>
-  </si>
-  <si>
-    <t>0.0670,0.0124,0.9266,0.0094</t>
-  </si>
-  <si>
-    <t>0.0468,0.0038,0.9459,0.0088</t>
-  </si>
-  <si>
-    <t>0.0148,0.0039,0.9635,0.0174</t>
-  </si>
-  <si>
-    <t>0.0074,0.0047,0.9900,0.0012</t>
-  </si>
-  <si>
-    <t>0.9581,0.0414,0.0010,0.0041</t>
-  </si>
-  <si>
-    <t>0.9691,0.0047,0.0005,0.0141</t>
-  </si>
-  <si>
-    <t>0.9722,0.0045,0.0007,0.0112</t>
-  </si>
-  <si>
-    <t>0.0012,0.0042,0.9912,0.0094</t>
-  </si>
-  <si>
-    <t>0.9796,0.0010,0.0002,0.0164</t>
-  </si>
-  <si>
-    <t>0.9897,0.0023,0.0002,0.0032</t>
-  </si>
-  <si>
-    <t>0.9696,0.0180,0.0005,0.0052</t>
-  </si>
-  <si>
-    <t>0.0101,0.8446,0.5909,0.0038</t>
-  </si>
-  <si>
-    <t>0.0008,0.0060,0.9826,0.0184</t>
-  </si>
-  <si>
-    <t>0.0032,0.0098,0.9858,0.0052</t>
-  </si>
-  <si>
-    <t>0.0019,0.5802,0.9654,0.0012</t>
-  </si>
-  <si>
-    <t>0.0009,0.0026,0.9895,0.0111</t>
-  </si>
-  <si>
-    <t>0.1185,0.8568,0.0235,0.0015</t>
-  </si>
-  <si>
-    <t>0.0204,0.9814,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.6482,0.0715,0.3842,0.0405</t>
-  </si>
-  <si>
-    <t>0.6580,0.2480,0.1338,0.0263</t>
-  </si>
-  <si>
-    <t>0.0231,0.0264,0.9639,0.0093</t>
-  </si>
-  <si>
-    <t>0.0033,0.7364,0.9052,0.0012</t>
-  </si>
-  <si>
-    <t>0.0083,0.3814,0.9483,0.0023</t>
-  </si>
-  <si>
-    <t>0.0042,0.9592,0.1232,0.0002</t>
-  </si>
-  <si>
-    <t>0.0032,0.6562,0.8792,0.0008</t>
-  </si>
-  <si>
-    <t>0.0892,0.0025,0.0640,0.8654</t>
-  </si>
-  <si>
-    <t>0.0096,0.0095,0.0029,0.9922</t>
-  </si>
-  <si>
-    <t>0.0112,0.0048,0.0020,0.9927</t>
-  </si>
-  <si>
-    <t>0.0502,0.0027,0.0074,0.9707</t>
-  </si>
-  <si>
-    <t>0.0278,0.0198,0.0066,0.9791</t>
-  </si>
-  <si>
-    <t>0.0393,0.0174,0.0144,0.9699</t>
-  </si>
-  <si>
-    <t>0.0015,0.8767,0.8680,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.1782,0.9772,0.0031</t>
-  </si>
-  <si>
-    <t>0.0136,0.0699,0.9479,0.0042</t>
-  </si>
-  <si>
-    <t>0.0171,0.5635,0.7135,0.0037</t>
-  </si>
-  <si>
-    <t>0.0042,0.7105,0.8253,0.0009</t>
-  </si>
-  <si>
-    <t>0.0057,0.8326,0.4877,0.0003</t>
-  </si>
-  <si>
-    <t>0.9702,0.0018,0.0014,0.0198</t>
-  </si>
-  <si>
-    <t>0.9807,0.0028,0.0003,0.0082</t>
-  </si>
-  <si>
-    <t>0.9870,0.0038,0.0005,0.0030</t>
-  </si>
-  <si>
-    <t>0.9901,0.0015,0.0002,0.0041</t>
-  </si>
-  <si>
-    <t>0.9823,0.0013,0.0002,0.0110</t>
-  </si>
-  <si>
-    <t>0.9866,0.0013,0.0003,0.0071</t>
-  </si>
-  <si>
-    <t>0.9795,0.0006,0.0001,0.0209</t>
-  </si>
-  <si>
-    <t>0.9896,0.0022,0.0003,0.0028</t>
-  </si>
-  <si>
-    <t>0.9821,0.0007,0.0002,0.0141</t>
-  </si>
-  <si>
-    <t>0.9887,0.0016,0.0004,0.0043</t>
-  </si>
-  <si>
-    <t>0.9743,0.0014,0.0006,0.0203</t>
-  </si>
-  <si>
-    <t>0.9893,0.0008,0.0002,0.0066</t>
-  </si>
-  <si>
-    <t>0.9864,0.0021,0.0002,0.0057</t>
-  </si>
-  <si>
-    <t>0.9905,0.0014,0.0002,0.0040</t>
-  </si>
-  <si>
-    <t>0.9824,0.0019,0.0003,0.0104</t>
-  </si>
-  <si>
-    <t>0.9823,0.0029,0.0003,0.0076</t>
-  </si>
-  <si>
-    <t>0.0001,0.0015,0.9947,0.0100</t>
-  </si>
-  <si>
-    <t>0.1767,0.0187,0.8453,0.0094</t>
-  </si>
-  <si>
-    <t>0.2468,0.0476,0.3484,0.4244</t>
-  </si>
-  <si>
-    <t>0.1349,0.0173,0.8788,0.0098</t>
-  </si>
-  <si>
-    <t>0.1533,0.8770,0.0038,0.0050</t>
-  </si>
-  <si>
-    <t>0.1747,0.8132,0.0015,0.0176</t>
-  </si>
-  <si>
-    <t>0.2683,0.8133,0.0012,0.0043</t>
-  </si>
-  <si>
-    <t>0.6544,0.5737,0.0023,0.0013</t>
-  </si>
-  <si>
-    <t>0.1279,0.8995,0.0053,0.0040</t>
-  </si>
-  <si>
-    <t>0.0387,0.9665,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.7085,0.5260,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.6531,0.0507,0.2348,0.0900</t>
-  </si>
-  <si>
-    <t>0.2669,0.0149,0.7895,0.0169</t>
-  </si>
-  <si>
-    <t>0.5354,0.0559,0.4763,0.0385</t>
-  </si>
-  <si>
-    <t>0.3708,0.2002,0.4543,0.1028</t>
-  </si>
-  <si>
-    <t>0.1046,0.0785,0.0282,0.9092</t>
-  </si>
-  <si>
-    <t>0.0112,0.9710,0.0212,0.0010</t>
-  </si>
-  <si>
-    <t>0.0139,0.9484,0.0619,0.0038</t>
-  </si>
-  <si>
-    <t>0.0383,0.9201,0.0205,0.0302</t>
-  </si>
-  <si>
-    <t>0.0014,0.9693,0.3475,0.0009</t>
-  </si>
-  <si>
-    <t>0.1259,0.9018,0.0150,0.0040</t>
-  </si>
-  <si>
-    <t>0.6702,0.5015,0.0086,0.0038</t>
-  </si>
-  <si>
-    <t>0.7787,0.3834,0.0057,0.0017</t>
-  </si>
-  <si>
-    <t>0.9616,0.0080,0.0023,0.0152</t>
-  </si>
-  <si>
-    <t>0.9753,0.0024,0.0021,0.0103</t>
-  </si>
-  <si>
-    <t>0.9682,0.0018,0.0005,0.0237</t>
-  </si>
-  <si>
-    <t>0.9823,0.0040,0.0009,0.0052</t>
-  </si>
-  <si>
-    <t>0.9747,0.0098,0.0026,0.0063</t>
-  </si>
-  <si>
-    <t>0.9031,0.1073,0.0042,0.0093</t>
-  </si>
-  <si>
-    <t>0.9560,0.0063,0.0021,0.0204</t>
-  </si>
-  <si>
-    <t>0.9721,0.0019,0.0019,0.0149</t>
-  </si>
-  <si>
-    <t>0.0037,0.4963,0.9398,0.0007</t>
-  </si>
-  <si>
-    <t>0.0092,0.6048,0.8157,0.0016</t>
-  </si>
-  <si>
-    <t>0.0131,0.1272,0.9419,0.0070</t>
-  </si>
-  <si>
-    <t>0.0127,0.0715,0.9632,0.0014</t>
-  </si>
-  <si>
-    <t>0.2994,0.0556,0.6772,0.0323</t>
-  </si>
-  <si>
-    <t>0.5152,0.0406,0.4769,0.0793</t>
-  </si>
-  <si>
-    <t>0.3517,0.0098,0.7668,0.0084</t>
-  </si>
-  <si>
-    <t>0.5059,0.0860,0.4700,0.0275</t>
-  </si>
-  <si>
-    <t>0.0243,0.0120,0.0042,0.9834</t>
-  </si>
-  <si>
-    <t>0.0020,0.0034,0.0008,0.9982</t>
-  </si>
-  <si>
-    <t>0.0083,0.0143,0.0048,0.9914</t>
-  </si>
-  <si>
-    <t>0.0245,0.0024,0.0030,0.9872</t>
-  </si>
-  <si>
-    <t>0.0011,0.8031,0.9353,0.0010</t>
-  </si>
-  <si>
-    <t>0.9343,0.0320,0.0162,0.0115</t>
-  </si>
-  <si>
-    <t>0.6205,0.4279,0.0063,0.0166</t>
-  </si>
-  <si>
-    <t>0.9678,0.0055,0.0016,0.0121</t>
-  </si>
-  <si>
-    <t>0.2737,0.7913,0.0141,0.0064</t>
-  </si>
-  <si>
-    <t>0.8704,0.0064,0.0102,0.0939</t>
-  </si>
-  <si>
-    <t>0.3988,0.0049,0.0079,0.7308</t>
-  </si>
-  <si>
-    <t>0.9284,0.0029,0.0007,0.0765</t>
-  </si>
-  <si>
-    <t>0.0010,0.0263,0.8833,0.2737</t>
-  </si>
-  <si>
-    <t>0.2724,0.0016,0.0087,0.8238</t>
-  </si>
-  <si>
-    <t>0.8790,0.0144,0.0019,0.0820</t>
-  </si>
-  <si>
-    <t>0.4415,0.5664,0.0550,0.0253</t>
-  </si>
-  <si>
-    <t>0.7015,0.2088,0.0361,0.0621</t>
-  </si>
-  <si>
-    <t>0.7534,0.1403,0.0473,0.0837</t>
-  </si>
-  <si>
-    <t>0.3580,0.6577,0.0164,0.0257</t>
-  </si>
-  <si>
-    <t>0.6985,0.1449,0.1953,0.0215</t>
-  </si>
-  <si>
-    <t>0.6456,0.2696,0.0367,0.0781</t>
-  </si>
-  <si>
-    <t>0.9657,0.0011,0.0003,0.0364</t>
-  </si>
-  <si>
-    <t>0.9683,0.0046,0.0009,0.0152</t>
-  </si>
-  <si>
-    <t>0.9810,0.0013,0.0002,0.0135</t>
-  </si>
-  <si>
-    <t>0.9539,0.0010,0.0008,0.0514</t>
-  </si>
-  <si>
-    <t>0.9598,0.0089,0.0009,0.0169</t>
-  </si>
-  <si>
-    <t>0.9636,0.0058,0.0030,0.0152</t>
-  </si>
-  <si>
-    <t>0.9608,0.0076,0.0013,0.0168</t>
-  </si>
-  <si>
-    <t>0.9826,0.0011,0.0003,0.0108</t>
-  </si>
-  <si>
-    <t>0.6752,0.5258,0.0056,0.0042</t>
-  </si>
-  <si>
-    <t>0.8726,0.2023,0.0078,0.0028</t>
-  </si>
-  <si>
-    <t>0.7654,0.2994,0.0064,0.0077</t>
-  </si>
-  <si>
-    <t>0.8299,0.0580,0.1461,0.0239</t>
-  </si>
-  <si>
-    <t>0.9361,0.0677,0.0023,0.0054</t>
-  </si>
-  <si>
-    <t>0.8984,0.0624,0.0149,0.0128</t>
-  </si>
-  <si>
-    <t>0.9493,0.0105,0.0017,0.0211</t>
-  </si>
-  <si>
-    <t>0.7819,0.1813,0.0517,0.0440</t>
-  </si>
-  <si>
-    <t>0.0007,0.0116,0.9956,0.0014</t>
-  </si>
-  <si>
-    <t>0.9499,0.0246,0.0055,0.0107</t>
-  </si>
-  <si>
-    <t>0.0077,0.0047,0.9897,0.0008</t>
-  </si>
-  <si>
-    <t>0.0035,0.2332,0.9709,0.0039</t>
-  </si>
-  <si>
-    <t>0.1714,0.0383,0.8218,0.0107</t>
-  </si>
-  <si>
-    <t>0.0164,0.0867,0.9504,0.0046</t>
-  </si>
-  <si>
-    <t>0.0012,0.0047,0.9940,0.0022</t>
-  </si>
-  <si>
-    <t>0.0047,0.0006,0.9886,0.0041</t>
-  </si>
-  <si>
-    <t>0.0016,0.0020,0.9955,0.0009</t>
-  </si>
-  <si>
-    <t>0.2532,0.0987,0.6592,0.0184</t>
-  </si>
-  <si>
-    <t>0.1572,0.0273,0.8489,0.0077</t>
-  </si>
-  <si>
-    <t>0.4994,0.1972,0.3514,0.0246</t>
-  </si>
-  <si>
-    <t>0.1009,0.4037,0.4343,0.0037</t>
-  </si>
-  <si>
-    <t>0.3570,0.0641,0.6332,0.0166</t>
-  </si>
-  <si>
-    <t>0.2003,0.5044,0.2473,0.0207</t>
-  </si>
-  <si>
-    <t>0.3003,0.1973,0.5692,0.0484</t>
-  </si>
-  <si>
-    <t>0.6572,0.2855,0.0740,0.0140</t>
-  </si>
-  <si>
-    <t>0.9107,0.1004,0.0084,0.0057</t>
-  </si>
-  <si>
-    <t>0.9710,0.0436,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.9462,0.0348,0.0081,0.0070</t>
-  </si>
-  <si>
-    <t>0.9563,0.0301,0.0065,0.0057</t>
-  </si>
-  <si>
-    <t>0.9465,0.0619,0.0012,0.0032</t>
-  </si>
-  <si>
-    <t>0.4155,0.1043,0.5102,0.0174</t>
-  </si>
-  <si>
-    <t>0.3843,0.0292,0.5756,0.0878</t>
-  </si>
-  <si>
-    <t>0.5324,0.0695,0.1312,0.2453</t>
-  </si>
-  <si>
-    <t>0.2300,0.0239,0.7822,0.0154</t>
-  </si>
-  <si>
-    <t>0.5193,0.0602,0.4860,0.0349</t>
-  </si>
-  <si>
-    <t>0.1182,0.0794,0.7501,0.1131</t>
-  </si>
-  <si>
-    <t>0.1523,0.0752,0.7646,0.0664</t>
-  </si>
-  <si>
-    <t>0.0084,0.0341,0.9474,0.0271</t>
-  </si>
-  <si>
-    <t>0.0596,0.0386,0.8772,0.0438</t>
-  </si>
-  <si>
-    <t>0.0169,0.1774,0.8565,0.0222</t>
-  </si>
-  <si>
-    <t>0.9827,0.0009,0.0002,0.0129</t>
-  </si>
-  <si>
-    <t>0.9786,0.0024,0.0005,0.0101</t>
-  </si>
-  <si>
-    <t>0.9821,0.0032,0.0003,0.0071</t>
-  </si>
-  <si>
-    <t>0.9855,0.0050,0.0008,0.0032</t>
-  </si>
-  <si>
-    <t>0.9815,0.0025,0.0002,0.0081</t>
-  </si>
-  <si>
-    <t>0.9841,0.0019,0.0004,0.0076</t>
-  </si>
-  <si>
-    <t>0.9725,0.0016,0.0003,0.0215</t>
-  </si>
-  <si>
-    <t>0.9814,0.0032,0.0004,0.0080</t>
-  </si>
-  <si>
-    <t>0.3818,0.0216,0.6789,0.0275</t>
-  </si>
-  <si>
-    <t>0.3538,0.0740,0.6513,0.0126</t>
-  </si>
-  <si>
-    <t>0.9114,0.0244,0.0044,0.0330</t>
-  </si>
-  <si>
-    <t>0.0031,0.0041,0.9858,0.0043</t>
-  </si>
-  <si>
-    <t>0.0023,0.0176,0.9907,0.0010</t>
-  </si>
-  <si>
-    <t>0.0047,0.0108,0.9885,0.0021</t>
-  </si>
-  <si>
-    <t>0.0007,0.0006,0.9897,0.0137</t>
-  </si>
-  <si>
-    <t>0.0792,0.0080,0.9134,0.0109</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9925,0.0181</t>
-  </si>
-  <si>
-    <t>0.0049,0.0056,0.9760,0.0092</t>
-  </si>
-  <si>
-    <t>0.4267,0.3683,0.2501,0.0508</t>
-  </si>
-  <si>
-    <t>0.2723,0.0409,0.6934,0.0392</t>
-  </si>
-  <si>
-    <t>0.2902,0.0168,0.7650,0.0256</t>
-  </si>
-  <si>
-    <t>0.5300,0.0214,0.1393,0.2789</t>
-  </si>
-  <si>
-    <t>0.9714,0.0027,0.0007,0.0183</t>
-  </si>
-  <si>
-    <t>0.9749,0.0033,0.0017,0.0125</t>
-  </si>
-  <si>
-    <t>0.9904,0.0028,0.0004,0.0023</t>
-  </si>
-  <si>
-    <t>0.9802,0.0064,0.0005,0.0055</t>
-  </si>
-  <si>
-    <t>0.9740,0.0031,0.0002,0.0131</t>
-  </si>
-  <si>
-    <t>0.9758,0.0022,0.0006,0.0158</t>
-  </si>
-  <si>
-    <t>0.9881,0.0019,0.0003,0.0049</t>
-  </si>
-  <si>
-    <t>0.9510,0.0058,0.0007,0.0294</t>
-  </si>
-  <si>
-    <t>0.0357,0.0428,0.9411,0.0017</t>
-  </si>
-  <si>
-    <t>0.0024,0.0447,0.9783,0.0074</t>
-  </si>
-  <si>
-    <t>0.0041,0.0100,0.9770,0.0116</t>
-  </si>
-  <si>
-    <t>0.0514,0.0550,0.8955,0.0015</t>
-  </si>
-  <si>
-    <t>0.0077,0.0027,0.9768,0.0127</t>
-  </si>
-  <si>
-    <t>0.4262,0.0624,0.4055,0.1519</t>
-  </si>
-  <si>
-    <t>0.1315,0.0096,0.6009,0.2657</t>
-  </si>
-  <si>
-    <t>0.0221,0.0113,0.9517,0.0157</t>
-  </si>
-  <si>
-    <t>0.4658,0.0074,0.0621,0.4777</t>
-  </si>
-  <si>
-    <t>0.0129,0.0554,0.0090,0.9834</t>
-  </si>
-  <si>
-    <t>0.1003,0.0032,0.0017,0.9627</t>
-  </si>
-  <si>
-    <t>0.0218,0.0025,0.0033,0.9869</t>
-  </si>
-  <si>
-    <t>0.0547,0.0015,0.0008,0.9821</t>
-  </si>
-  <si>
-    <t>0.4071,0.0318,0.0896,0.5539</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.3083,0.2117,0.0196,0.5584</t>
+  </si>
+  <si>
+    <t>0.0337,0.0060,0.0033,0.9817</t>
+  </si>
+  <si>
+    <t>0.1768,0.0235,0.0014,0.8820</t>
+  </si>
+  <si>
+    <t>0.0487,0.0087,0.0045,0.9733</t>
+  </si>
+  <si>
+    <t>0.9916,0.0005,0.0001,0.0057</t>
+  </si>
+  <si>
+    <t>0.9909,0.0014,0.0001,0.0036</t>
+  </si>
+  <si>
+    <t>0.9726,0.0056,0.0027,0.0113</t>
+  </si>
+  <si>
+    <t>0.9867,0.0013,0.0004,0.0063</t>
+  </si>
+  <si>
+    <t>0.9657,0.0077,0.0020,0.0151</t>
+  </si>
+  <si>
+    <t>0.9913,0.0022,0.0001,0.0027</t>
+  </si>
+  <si>
+    <t>0.9898,0.0012,0.0003,0.0040</t>
+  </si>
+  <si>
+    <t>0.9927,0.0007,0.0001,0.0035</t>
+  </si>
+  <si>
+    <t>0.4214,0.2260,0.4761,0.1069</t>
+  </si>
+  <si>
+    <t>0.1432,0.0358,0.8701,0.0075</t>
+  </si>
+  <si>
+    <t>0.2476,0.0471,0.7568,0.0095</t>
+  </si>
+  <si>
+    <t>0.3447,0.0293,0.6318,0.0687</t>
+  </si>
+  <si>
+    <t>0.6757,0.1685,0.0926,0.0835</t>
+  </si>
+  <si>
+    <t>0.1215,0.9230,0.0020,0.0015</t>
+  </si>
+  <si>
+    <t>0.0612,0.9540,0.0038,0.0004</t>
+  </si>
+  <si>
+    <t>0.6658,0.5306,0.0053,0.0021</t>
+  </si>
+  <si>
+    <t>0.4216,0.7249,0.0164,0.0014</t>
+  </si>
+  <si>
+    <t>0.1211,0.9253,0.0043,0.0011</t>
+  </si>
+  <si>
+    <t>0.4250,0.0720,0.2082,0.3409</t>
+  </si>
+  <si>
+    <t>0.0710,0.0023,0.7791,0.1092</t>
+  </si>
+  <si>
+    <t>0.0067,0.0010,0.9645,0.0291</t>
+  </si>
+  <si>
+    <t>0.1095,0.0398,0.8423,0.0141</t>
+  </si>
+  <si>
+    <t>0.0200,0.0065,0.9681,0.0059</t>
+  </si>
+  <si>
+    <t>0.2287,0.0087,0.8132,0.0141</t>
+  </si>
+  <si>
+    <t>0.0016,0.0008,0.9946,0.0020</t>
+  </si>
+  <si>
+    <t>0.2275,0.8340,0.0119,0.0041</t>
+  </si>
+  <si>
+    <t>0.5947,0.0998,0.3978,0.0469</t>
+  </si>
+  <si>
+    <t>0.0002,0.0013,0.9914,0.0381</t>
+  </si>
+  <si>
+    <t>0.0771,0.8670,0.0918,0.0039</t>
+  </si>
+  <si>
+    <t>0.6518,0.1863,0.1019,0.1250</t>
+  </si>
+  <si>
+    <t>0.1510,0.0356,0.8435,0.0244</t>
+  </si>
+  <si>
+    <t>0.8810,0.1732,0.0078,0.0068</t>
+  </si>
+  <si>
+    <t>0.0921,0.8182,0.2766,0.0299</t>
+  </si>
+  <si>
+    <t>0.0153,0.6410,0.6811,0.0440</t>
+  </si>
+  <si>
+    <t>0.0482,0.0384,0.7914,0.1625</t>
+  </si>
+  <si>
+    <t>0.0769,0.0317,0.8581,0.0488</t>
+  </si>
+  <si>
+    <t>0.0765,0.0210,0.5021,0.5289</t>
+  </si>
+  <si>
+    <t>0.0275,0.1444,0.9212,0.0089</t>
+  </si>
+  <si>
+    <t>0.0192,0.9246,0.1053,0.0032</t>
+  </si>
+  <si>
+    <t>0.0156,0.1181,0.9266,0.0160</t>
+  </si>
+  <si>
+    <t>0.0980,0.0834,0.0333,0.9085</t>
+  </si>
+  <si>
+    <t>0.0180,0.9476,0.0336,0.0075</t>
+  </si>
+  <si>
+    <t>0.0190,0.9498,0.0442,0.0058</t>
+  </si>
+  <si>
+    <t>0.0071,0.9656,0.0908,0.0046</t>
+  </si>
+  <si>
+    <t>0.0163,0.4878,0.8974,0.0096</t>
+  </si>
+  <si>
+    <t>0.0015,0.0876,0.9882,0.0018</t>
+  </si>
+  <si>
+    <t>0.1052,0.0258,0.8566,0.0267</t>
+  </si>
+  <si>
+    <t>0.0193,0.0070,0.9693,0.0072</t>
+  </si>
+  <si>
+    <t>0.0044,0.0033,0.9851,0.0062</t>
+  </si>
+  <si>
+    <t>0.0424,0.0210,0.9378,0.0099</t>
+  </si>
+  <si>
+    <t>0.9572,0.0305,0.0018,0.0068</t>
+  </si>
+  <si>
+    <t>0.9375,0.0608,0.0081,0.0046</t>
+  </si>
+  <si>
+    <t>0.9226,0.0392,0.0010,0.0183</t>
+  </si>
+  <si>
+    <t>0.0011,0.0060,0.9884,0.0128</t>
+  </si>
+  <si>
+    <t>0.9599,0.0090,0.0021,0.0161</t>
+  </si>
+  <si>
+    <t>0.9852,0.0079,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9570,0.0311,0.0033,0.0065</t>
+  </si>
+  <si>
+    <t>0.0020,0.8725,0.8873,0.0008</t>
+  </si>
+  <si>
+    <t>0.0014,0.0104,0.9714,0.0331</t>
+  </si>
+  <si>
+    <t>0.0115,0.0739,0.9142,0.0265</t>
+  </si>
+  <si>
+    <t>0.0006,0.9052,0.9498,0.0003</t>
+  </si>
+  <si>
+    <t>0.0058,0.0120,0.9801,0.0066</t>
+  </si>
+  <si>
+    <t>0.0975,0.8328,0.0485,0.0020</t>
+  </si>
+  <si>
+    <t>0.0076,0.9909,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.3081,0.0414,0.7642,0.0052</t>
+  </si>
+  <si>
+    <t>0.6799,0.3205,0.0542,0.0260</t>
+  </si>
+  <si>
+    <t>0.0035,0.0122,0.9835,0.0091</t>
+  </si>
+  <si>
+    <t>0.0096,0.2963,0.9463,0.0022</t>
+  </si>
+  <si>
+    <t>0.0096,0.7405,0.7888,0.0022</t>
+  </si>
+  <si>
+    <t>0.0040,0.9024,0.4940,0.0023</t>
+  </si>
+  <si>
+    <t>0.0019,0.7769,0.9269,0.0018</t>
+  </si>
+  <si>
+    <t>0.0592,0.0035,0.0779,0.8963</t>
+  </si>
+  <si>
+    <t>0.0107,0.0026,0.0007,0.9946</t>
+  </si>
+  <si>
+    <t>0.0150,0.0012,0.0008,0.9938</t>
+  </si>
+  <si>
+    <t>0.0816,0.0058,0.0029,0.9631</t>
+  </si>
+  <si>
+    <t>0.0412,0.0095,0.0053,0.9755</t>
+  </si>
+  <si>
+    <t>0.0263,0.0247,0.0088,0.9772</t>
+  </si>
+  <si>
+    <t>0.0048,0.8937,0.6961,0.0015</t>
+  </si>
+  <si>
+    <t>0.0021,0.5771,0.9644,0.0014</t>
+  </si>
+  <si>
+    <t>0.0104,0.1734,0.9500,0.0027</t>
+  </si>
+  <si>
+    <t>0.0129,0.0497,0.9612,0.0080</t>
+  </si>
+  <si>
+    <t>0.0026,0.9180,0.4759,0.0003</t>
+  </si>
+  <si>
+    <t>0.0140,0.5276,0.8901,0.0067</t>
+  </si>
+  <si>
+    <t>0.9867,0.0027,0.0010,0.0045</t>
+  </si>
+  <si>
+    <t>0.9825,0.0133,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.9861,0.0098,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9830,0.0025,0.0007,0.0069</t>
+  </si>
+  <si>
+    <t>0.9752,0.0032,0.0005,0.0138</t>
+  </si>
+  <si>
+    <t>0.9870,0.0021,0.0003,0.0053</t>
+  </si>
+  <si>
+    <t>0.9825,0.0038,0.0004,0.0064</t>
+  </si>
+  <si>
+    <t>0.9837,0.0044,0.0009,0.0047</t>
+  </si>
+  <si>
+    <t>0.9800,0.0010,0.0003,0.0149</t>
+  </si>
+  <si>
+    <t>0.9927,0.0011,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.9899,0.0007,0.0002,0.0063</t>
+  </si>
+  <si>
+    <t>0.9875,0.0016,0.0001,0.0060</t>
+  </si>
+  <si>
+    <t>0.9871,0.0010,0.0002,0.0075</t>
+  </si>
+  <si>
+    <t>0.9883,0.0023,0.0005,0.0041</t>
+  </si>
+  <si>
+    <t>0.9868,0.0011,0.0002,0.0074</t>
+  </si>
+  <si>
+    <t>0.9869,0.0005,0.0000,0.0105</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.9765,0.0993</t>
+  </si>
+  <si>
+    <t>0.0911,0.0214,0.8745,0.0205</t>
+  </si>
+  <si>
+    <t>0.4803,0.0929,0.4962,0.0506</t>
+  </si>
+  <si>
+    <t>0.0253,0.0018,0.9637,0.0085</t>
+  </si>
+  <si>
+    <t>0.1447,0.8556,0.0025,0.0121</t>
+  </si>
+  <si>
+    <t>0.1715,0.8781,0.0026,0.0031</t>
+  </si>
+  <si>
+    <t>0.4491,0.7023,0.0038,0.0054</t>
+  </si>
+  <si>
+    <t>0.2182,0.8805,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.3574,0.7487,0.0063,0.0085</t>
+  </si>
+  <si>
+    <t>0.0075,0.9845,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.7233,0.4424,0.0038,0.0040</t>
+  </si>
+  <si>
+    <t>0.4082,0.2000,0.4450,0.0333</t>
+  </si>
+  <si>
+    <t>0.1371,0.0187,0.8753,0.0115</t>
+  </si>
+  <si>
+    <t>0.2229,0.3141,0.3988,0.0105</t>
+  </si>
+  <si>
+    <t>0.5328,0.0876,0.4196,0.0771</t>
+  </si>
+  <si>
+    <t>0.0893,0.4121,0.0936,0.7970</t>
+  </si>
+  <si>
+    <t>0.0119,0.9711,0.0474,0.0018</t>
+  </si>
+  <si>
+    <t>0.0079,0.9724,0.0209,0.0057</t>
+  </si>
+  <si>
+    <t>0.2194,0.6893,0.0782,0.1350</t>
+  </si>
+  <si>
+    <t>0.0009,0.9704,0.4763,0.0023</t>
+  </si>
+  <si>
+    <t>0.2263,0.7973,0.0632,0.0062</t>
+  </si>
+  <si>
+    <t>0.6562,0.4203,0.0373,0.0084</t>
+  </si>
+  <si>
+    <t>0.8668,0.2086,0.0089,0.0021</t>
+  </si>
+  <si>
+    <t>0.9591,0.0061,0.0098,0.0133</t>
+  </si>
+  <si>
+    <t>0.9532,0.0221,0.0064,0.0102</t>
+  </si>
+  <si>
+    <t>0.9678,0.0011,0.0005,0.0302</t>
+  </si>
+  <si>
+    <t>0.9748,0.0025,0.0008,0.0135</t>
+  </si>
+  <si>
+    <t>0.9711,0.0051,0.0051,0.0112</t>
+  </si>
+  <si>
+    <t>0.9013,0.0494,0.0068,0.0227</t>
+  </si>
+  <si>
+    <t>0.9386,0.0019,0.0017,0.0656</t>
+  </si>
+  <si>
+    <t>0.9790,0.0030,0.0022,0.0075</t>
+  </si>
+  <si>
+    <t>0.0054,0.5106,0.9293,0.0030</t>
+  </si>
+  <si>
+    <t>0.0020,0.6329,0.9484,0.0008</t>
+  </si>
+  <si>
+    <t>0.0140,0.3013,0.9004,0.0055</t>
+  </si>
+  <si>
+    <t>0.0519,0.0468,0.8942,0.0052</t>
+  </si>
+  <si>
+    <t>0.4066,0.3976,0.1170,0.2072</t>
+  </si>
+  <si>
+    <t>0.5532,0.0474,0.5025,0.0312</t>
+  </si>
+  <si>
+    <t>0.4414,0.0248,0.6641,0.0177</t>
+  </si>
+  <si>
+    <t>0.4901,0.2537,0.2640,0.0244</t>
+  </si>
+  <si>
+    <t>0.0592,0.0031,0.0013,0.9778</t>
+  </si>
+  <si>
+    <t>0.0016,0.0099,0.0035,0.9968</t>
+  </si>
+  <si>
+    <t>0.0094,0.0023,0.0033,0.9928</t>
+  </si>
+  <si>
+    <t>0.0073,0.0099,0.0020,0.9939</t>
+  </si>
+  <si>
+    <t>0.0182,0.8829,0.3170,0.0044</t>
+  </si>
+  <si>
+    <t>0.9790,0.0058,0.0005,0.0061</t>
+  </si>
+  <si>
+    <t>0.7939,0.1259,0.0302,0.0535</t>
+  </si>
+  <si>
+    <t>0.9729,0.0052,0.0006,0.0107</t>
+  </si>
+  <si>
+    <t>0.9184,0.0464,0.0018,0.0150</t>
+  </si>
+  <si>
+    <t>0.9557,0.0082,0.0118,0.0130</t>
+  </si>
+  <si>
+    <t>0.6504,0.0086,0.0326,0.2647</t>
+  </si>
+  <si>
+    <t>0.8224,0.0013,0.0011,0.2858</t>
+  </si>
+  <si>
+    <t>0.0006,0.0230,0.9582,0.0962</t>
+  </si>
+  <si>
+    <t>0.7390,0.0015,0.0171,0.2167</t>
+  </si>
+  <si>
+    <t>0.6647,0.0032,0.0147,0.3284</t>
+  </si>
+  <si>
+    <t>0.1675,0.7705,0.0308,0.0674</t>
+  </si>
+  <si>
+    <t>0.5557,0.5148,0.0301,0.0231</t>
+  </si>
+  <si>
+    <t>0.7565,0.1566,0.0621,0.0470</t>
+  </si>
+  <si>
+    <t>0.4580,0.4433,0.1290,0.0376</t>
+  </si>
+  <si>
+    <t>0.8780,0.0492,0.0403,0.0115</t>
+  </si>
+  <si>
+    <t>0.6880,0.3169,0.0433,0.0209</t>
+  </si>
+  <si>
+    <t>0.9754,0.0007,0.0002,0.0251</t>
+  </si>
+  <si>
+    <t>0.9254,0.0071,0.0024,0.0536</t>
+  </si>
+  <si>
+    <t>0.9772,0.0045,0.0007,0.0090</t>
+  </si>
+  <si>
+    <t>0.9059,0.0011,0.0015,0.1300</t>
+  </si>
+  <si>
+    <t>0.9758,0.0021,0.0002,0.0154</t>
+  </si>
+  <si>
+    <t>0.9727,0.0018,0.0006,0.0198</t>
+  </si>
+  <si>
+    <t>0.9817,0.0026,0.0004,0.0087</t>
+  </si>
+  <si>
+    <t>0.9721,0.0037,0.0014,0.0132</t>
+  </si>
+  <si>
+    <t>0.6557,0.4713,0.0037,0.0080</t>
+  </si>
+  <si>
+    <t>0.7984,0.1928,0.0091,0.0170</t>
+  </si>
+  <si>
+    <t>0.7735,0.3004,0.0023,0.0067</t>
+  </si>
+  <si>
+    <t>0.0663,0.0503,0.9338,0.0030</t>
+  </si>
+  <si>
+    <t>0.8954,0.1483,0.0014,0.0052</t>
+  </si>
+  <si>
+    <t>0.9196,0.0346,0.0225,0.0116</t>
+  </si>
+  <si>
+    <t>0.9183,0.0937,0.0026,0.0052</t>
+  </si>
+  <si>
+    <t>0.9135,0.0366,0.0049,0.0256</t>
+  </si>
+  <si>
+    <t>0.0017,0.0046,0.9944,0.0018</t>
+  </si>
+  <si>
+    <t>0.9606,0.0093,0.0082,0.0088</t>
+  </si>
+  <si>
+    <t>0.0034,0.0033,0.9872,0.0064</t>
+  </si>
+  <si>
+    <t>0.0066,0.0287,0.9843,0.0015</t>
+  </si>
+  <si>
+    <t>0.0551,0.0094,0.9485,0.0049</t>
+  </si>
+  <si>
+    <t>0.0055,0.0289,0.9433,0.0422</t>
+  </si>
+  <si>
+    <t>0.0366,0.0111,0.9681,0.0027</t>
+  </si>
+  <si>
+    <t>0.0144,0.0016,0.9843,0.0016</t>
+  </si>
+  <si>
+    <t>0.0039,0.0059,0.9888,0.0026</t>
+  </si>
+  <si>
+    <t>0.3177,0.2354,0.4904,0.0358</t>
+  </si>
+  <si>
+    <t>0.3347,0.1154,0.5729,0.0324</t>
+  </si>
+  <si>
+    <t>0.2587,0.1659,0.5814,0.0175</t>
+  </si>
+  <si>
+    <t>0.3288,0.0845,0.6197,0.0113</t>
+  </si>
+  <si>
+    <t>0.1056,0.1809,0.6865,0.0075</t>
+  </si>
+  <si>
+    <t>0.5048,0.0428,0.5438,0.0044</t>
+  </si>
+  <si>
+    <t>0.3807,0.3539,0.3037,0.0416</t>
+  </si>
+  <si>
+    <t>0.3235,0.0451,0.6574,0.0146</t>
+  </si>
+  <si>
+    <t>0.9352,0.0910,0.0022,0.0038</t>
+  </si>
+  <si>
+    <t>0.8011,0.3126,0.0111,0.0025</t>
+  </si>
+  <si>
+    <t>0.9100,0.0668,0.0349,0.0063</t>
+  </si>
+  <si>
+    <t>0.9492,0.0206,0.0013,0.0129</t>
+  </si>
+  <si>
+    <t>0.9711,0.0158,0.0008,0.0053</t>
+  </si>
+  <si>
+    <t>0.5032,0.1889,0.3095,0.0083</t>
+  </si>
+  <si>
+    <t>0.5558,0.0266,0.4694,0.0452</t>
+  </si>
+  <si>
+    <t>0.3589,0.0549,0.2107,0.4145</t>
+  </si>
+  <si>
+    <t>0.2959,0.0226,0.7105,0.0484</t>
+  </si>
+  <si>
+    <t>0.4224,0.0625,0.5036,0.1213</t>
+  </si>
+  <si>
+    <t>0.0329,0.0405,0.8893,0.0652</t>
+  </si>
+  <si>
+    <t>0.0503,0.0847,0.8813,0.0159</t>
+  </si>
+  <si>
+    <t>0.0108,0.0185,0.9616,0.0166</t>
+  </si>
+  <si>
+    <t>0.0594,0.1106,0.8698,0.0118</t>
+  </si>
+  <si>
+    <t>0.0316,0.3780,0.7516,0.0043</t>
+  </si>
+  <si>
+    <t>0.9794,0.0013,0.0002,0.0147</t>
+  </si>
+  <si>
+    <t>0.9832,0.0076,0.0009,0.0028</t>
+  </si>
+  <si>
+    <t>0.9734,0.0045,0.0006,0.0114</t>
+  </si>
+  <si>
+    <t>0.9886,0.0032,0.0004,0.0030</t>
+  </si>
+  <si>
+    <t>0.9814,0.0021,0.0003,0.0093</t>
+  </si>
+  <si>
+    <t>0.9864,0.0098,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.9764,0.0010,0.0001,0.0200</t>
+  </si>
+  <si>
+    <t>0.9795,0.0063,0.0006,0.0067</t>
+  </si>
+  <si>
+    <t>0.3061,0.0241,0.7614,0.0308</t>
+  </si>
+  <si>
+    <t>0.4921,0.3664,0.1426,0.0056</t>
+  </si>
+  <si>
+    <t>0.9021,0.0745,0.0085,0.0148</t>
+  </si>
+  <si>
+    <t>0.0005,0.0039,0.9965,0.0012</t>
+  </si>
+  <si>
+    <t>0.0011,0.0095,0.9913,0.0026</t>
+  </si>
+  <si>
+    <t>0.0010,0.0044,0.9944,0.0015</t>
+  </si>
+  <si>
+    <t>0.0007,0.0021,0.9946,0.0027</t>
+  </si>
+  <si>
+    <t>0.0739,0.2276,0.6703,0.0077</t>
+  </si>
+  <si>
+    <t>0.0006,0.0033,0.9887,0.0173</t>
+  </si>
+  <si>
+    <t>0.0081,0.0095,0.9784,0.0050</t>
+  </si>
+  <si>
+    <t>0.2119,0.2454,0.4992,0.0152</t>
+  </si>
+  <si>
+    <t>0.3217,0.0156,0.6317,0.0761</t>
+  </si>
+  <si>
+    <t>0.3788,0.0628,0.6153,0.0276</t>
+  </si>
+  <si>
+    <t>0.3301,0.0372,0.7026,0.0193</t>
+  </si>
+  <si>
+    <t>0.9549,0.0022,0.0006,0.0482</t>
+  </si>
+  <si>
+    <t>0.9887,0.0025,0.0005,0.0035</t>
+  </si>
+  <si>
+    <t>0.9875,0.0013,0.0005,0.0059</t>
+  </si>
+  <si>
+    <t>0.9717,0.0021,0.0007,0.0178</t>
+  </si>
+  <si>
+    <t>0.9831,0.0016,0.0002,0.0100</t>
+  </si>
+  <si>
+    <t>0.9834,0.0043,0.0006,0.0049</t>
+  </si>
+  <si>
+    <t>0.9883,0.0050,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.9729,0.0038,0.0006,0.0118</t>
+  </si>
+  <si>
+    <t>0.0191,0.2194,0.8920,0.0077</t>
+  </si>
+  <si>
+    <t>0.0199,0.1662,0.9168,0.0097</t>
+  </si>
+  <si>
+    <t>0.0067,0.0322,0.9743,0.0044</t>
+  </si>
+  <si>
+    <t>0.1857,0.1660,0.6071,0.0126</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.9885,0.0198</t>
+  </si>
+  <si>
+    <t>0.1792,0.0340,0.2059,0.6557</t>
+  </si>
+  <si>
+    <t>0.1671,0.0137,0.8308,0.0223</t>
+  </si>
+  <si>
+    <t>0.0128,0.0066,0.8573,0.1776</t>
+  </si>
+  <si>
+    <t>0.7213,0.0077,0.0029,0.3328</t>
+  </si>
+  <si>
+    <t>0.0143,0.0895,0.0114,0.9777</t>
+  </si>
+  <si>
+    <t>0.1132,0.0068,0.0063,0.9424</t>
+  </si>
+  <si>
+    <t>0.0371,0.0022,0.0019,0.9840</t>
+  </si>
+  <si>
+    <t>0.0095,0.0012,0.0005,0.9956</t>
+  </si>
+  <si>
+    <t>0.5780,0.0357,0.0614,0.3481</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2584,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2959,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3897,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4040,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,10 +4177,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4793,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5202,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5213,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
